--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553300.55764852</v>
+        <v>553301</v>
       </c>
       <c r="R2" t="n">
-        <v>6835184.143786674</v>
+        <v>6835184</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,19 +768,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,12 +786,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -811,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -868,10 +858,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553241.2079668331</v>
+        <v>553241</v>
       </c>
       <c r="R3" t="n">
-        <v>6835143.300850938</v>
+        <v>6835143</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,19 +891,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,12 +919,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -954,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +991,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553285.4370830621</v>
+        <v>553285</v>
       </c>
       <c r="R4" t="n">
-        <v>6835207.675594461</v>
+        <v>6835208</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1044,19 +1024,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,12 +1052,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1097,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1154,10 +1124,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553269.3022117999</v>
+        <v>553269</v>
       </c>
       <c r="R5" t="n">
-        <v>6835142.783994451</v>
+        <v>6835143</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1187,19 +1157,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1225,12 +1185,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1240,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1297,10 +1257,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553290.4739242411</v>
+        <v>553290</v>
       </c>
       <c r="R6" t="n">
-        <v>6835220.586682212</v>
+        <v>6835221</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1330,19 +1290,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1368,12 +1318,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1383,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1440,10 +1390,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553285.1874783114</v>
+        <v>553285</v>
       </c>
       <c r="R7" t="n">
-        <v>6835223.832143187</v>
+        <v>6835224</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1473,19 +1423,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1511,12 +1451,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1526,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1583,10 +1523,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553278.0928131961</v>
+        <v>553278</v>
       </c>
       <c r="R8" t="n">
-        <v>6835220.870713392</v>
+        <v>6835221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1616,19 +1556,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1654,12 +1584,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1669,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1726,10 +1656,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553297.5479298893</v>
+        <v>553298</v>
       </c>
       <c r="R9" t="n">
-        <v>6835194.078782379</v>
+        <v>6835194</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1759,19 +1689,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1797,12 +1717,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1812,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1865,10 +1785,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553144.3462572343</v>
+        <v>553144</v>
       </c>
       <c r="R10" t="n">
-        <v>6835157.96774963</v>
+        <v>6835158</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1898,19 +1818,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1926,12 +1836,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1941,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1994,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553168.0032188112</v>
+        <v>553168</v>
       </c>
       <c r="R11" t="n">
-        <v>6835167.363277408</v>
+        <v>6835167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2027,19 +1937,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2055,12 +1955,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2070,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2123,10 +2023,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553307.2043658107</v>
+        <v>553307</v>
       </c>
       <c r="R12" t="n">
-        <v>6835216.092161599</v>
+        <v>6835216</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2156,19 +2056,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2189,12 +2079,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2204,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2257,10 +2147,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553304.4737235887</v>
+        <v>553304</v>
       </c>
       <c r="R13" t="n">
-        <v>6835207.969746494</v>
+        <v>6835208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2290,19 +2180,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2318,12 +2198,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2333,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2386,10 +2266,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553128.9337335289</v>
+        <v>553129</v>
       </c>
       <c r="R14" t="n">
-        <v>6835169.613119329</v>
+        <v>6835170</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2419,19 +2299,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2447,12 +2317,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2462,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2515,10 +2385,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553247.8406454186</v>
+        <v>553248</v>
       </c>
       <c r="R15" t="n">
-        <v>6835176.199872245</v>
+        <v>6835176</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2548,19 +2418,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2581,12 +2441,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2596,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2649,10 +2509,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553256.256400865</v>
+        <v>553256</v>
       </c>
       <c r="R16" t="n">
-        <v>6835309.414410581</v>
+        <v>6835309</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2682,19 +2542,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2715,12 +2565,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2730,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2783,10 +2633,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553052.3972968218</v>
+        <v>553052</v>
       </c>
       <c r="R17" t="n">
-        <v>6835131.835866421</v>
+        <v>6835132</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2816,19 +2666,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2849,12 +2689,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2864,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2917,10 +2757,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553305.2566418765</v>
+        <v>553305</v>
       </c>
       <c r="R18" t="n">
-        <v>6835218.913894441</v>
+        <v>6835219</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2950,19 +2790,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2983,12 +2813,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2998,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3051,10 +2881,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553257.8202975453</v>
+        <v>553258</v>
       </c>
       <c r="R19" t="n">
-        <v>6835177.304575486</v>
+        <v>6835177</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3084,19 +2914,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3112,12 +2932,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3127,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3184,10 +3004,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553079.5999635729</v>
+        <v>553080</v>
       </c>
       <c r="R20" t="n">
-        <v>6835220.18681554</v>
+        <v>6835220</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3217,19 +3037,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3260,12 +3070,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3275,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3328,10 +3138,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553255.8359071156</v>
+        <v>553256</v>
       </c>
       <c r="R21" t="n">
-        <v>6835182.502354077</v>
+        <v>6835183</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3361,19 +3171,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3389,12 +3189,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3404,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3445,10 +3245,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553236.4648461207</v>
+        <v>553236</v>
       </c>
       <c r="R22" t="n">
-        <v>6835358.063690718</v>
+        <v>6835358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3478,19 +3278,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3506,12 +3296,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3521,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>93044</v>
+        <v>94771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3570,10 +3360,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553102.4785238563</v>
+        <v>553102</v>
       </c>
       <c r="R23" t="n">
-        <v>6835063.68494942</v>
+        <v>6835064</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3603,19 +3393,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3641,12 +3421,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3656,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3713,10 +3493,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553092.8057177188</v>
+        <v>553093</v>
       </c>
       <c r="R24" t="n">
-        <v>6835042.621640898</v>
+        <v>6835043</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3746,19 +3526,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3784,12 +3554,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3799,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3852,10 +3622,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>553215.3540575525</v>
+        <v>553215</v>
       </c>
       <c r="R25" t="n">
-        <v>6835152.883483743</v>
+        <v>6835153</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3885,19 +3655,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3913,12 +3673,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3928,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3981,10 +3741,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553160.2494580678</v>
+        <v>553160</v>
       </c>
       <c r="R26" t="n">
-        <v>6835145.379338398</v>
+        <v>6835145</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4014,19 +3774,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -4047,12 +3797,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4062,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4115,10 +3865,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553279.5437942485</v>
+        <v>553280</v>
       </c>
       <c r="R27" t="n">
-        <v>6835188.572216306</v>
+        <v>6835189</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4148,19 +3898,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4181,12 +3921,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4196,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4253,10 +3993,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553296.6181226404</v>
+        <v>553297</v>
       </c>
       <c r="R28" t="n">
-        <v>6835192.638487128</v>
+        <v>6835193</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4286,19 +4026,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4329,12 +4059,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4344,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4397,10 +4127,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>553166.1801062527</v>
+        <v>553166</v>
       </c>
       <c r="R29" t="n">
-        <v>6835162.106737893</v>
+        <v>6835162</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4430,19 +4160,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4458,12 +4178,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4473,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4526,10 +4246,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>553199.8176473408</v>
+        <v>553200</v>
       </c>
       <c r="R30" t="n">
-        <v>6835110.815906374</v>
+        <v>6835111</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4559,19 +4279,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4587,12 +4297,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Bo  Henriksson, Jens Hansen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4602,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>78527</v>
+        <v>79812</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4650,10 +4360,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>553143.9215631348</v>
+        <v>553144</v>
       </c>
       <c r="R31" t="n">
-        <v>6835092.842674972</v>
+        <v>6835093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4683,19 +4393,9 @@
           <t>2021-08-02</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4726,12 +4426,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,12 +919,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1052,12 +1052,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1185,12 +1185,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1451,12 +1451,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1584,12 +1584,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1717,12 +1717,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1955,12 +1955,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2079,12 +2079,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2198,12 +2198,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2317,12 +2317,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2565,12 +2565,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2813,12 +2813,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2932,12 +2932,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3189,12 +3189,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3296,12 +3296,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3421,12 +3421,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3554,12 +3554,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3673,12 +3673,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3797,12 +3797,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3921,12 +3921,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4059,12 +4059,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4178,12 +4178,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4297,12 +4297,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo  Henriksson, Jens Hansen</t>
+          <t>Carina Frost, Jens Hansen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79812</v>
+        <v>79813</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4426,12 +4426,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94777</v>
+        <v>94780</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79813</v>
+        <v>79816</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94780</v>
+        <v>94797</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79816</v>
+        <v>79822</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94797</v>
+        <v>94803</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79822</v>
+        <v>79827</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94803</v>
+        <v>94805</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79827</v>
+        <v>79829</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>95263400</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>95264460</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>95264089</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>95264522</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>95264049</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>95264194</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>95264257</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>95263872</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>95386244</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
         <v>95386183</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
         <v>95386114</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
         <v>95386099</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2213,7 +2213,7 @@
         <v>95386259</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         <v>95386456</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2456,7 +2456,7 @@
         <v>95386154</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
         <v>95386313</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2704,7 +2704,7 @@
         <v>95386133</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>95386487</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2947,7 +2947,7 @@
         <v>95264356</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>95386500</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3204,7 +3204,7 @@
         <v>95386164</v>
       </c>
       <c r="B22" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3311,7 +3311,7 @@
         <v>95264703</v>
       </c>
       <c r="B23" t="n">
-        <v>94805</v>
+        <v>95313</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>95264424</v>
       </c>
       <c r="B24" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>95386390</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3688,7 +3688,7 @@
         <v>95386224</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3812,7 +3812,7 @@
         <v>95386517</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3936,7 +3936,7 @@
         <v>95263753</v>
       </c>
       <c r="B28" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
         <v>95386200</v>
       </c>
       <c r="B29" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4193,7 +4193,7 @@
         <v>95386375</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carina Frost, Jens Hansen</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -675,70 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95263400</v>
+        <v>95264703</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553301</v>
+        <v>553102</v>
       </c>
       <c r="R2" t="n">
-        <v>6835184</v>
+        <v>6835064</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,6 +769,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -798,70 +795,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95264460</v>
+        <v>95386164</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553241</v>
+        <v>553236</v>
       </c>
       <c r="R3" t="n">
-        <v>6835143</v>
+        <v>6835358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,16 +882,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -924,22 +890,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95264089</v>
+        <v>95263400</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553285</v>
+        <v>553301</v>
       </c>
       <c r="R4" t="n">
-        <v>6835208</v>
+        <v>6835184</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,16 +999,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1064,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95264522</v>
+        <v>95263753</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1124,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553269</v>
+        <v>553297</v>
       </c>
       <c r="R5" t="n">
-        <v>6835143</v>
+        <v>6835193</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,6 +1106,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>28 blommande stjälkar inom ca 20 m2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,22 +1141,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95264049</v>
+        <v>95263872</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1232,7 +1178,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1257,13 +1203,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553290</v>
+        <v>553298</v>
       </c>
       <c r="R6" t="n">
-        <v>6835221</v>
+        <v>6835194</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1330,15 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95264194</v>
+        <v>95264049</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1386,17 +1327,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grönås !9:1 Vid Rotfarsdalen, Hls</t>
+          <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553285</v>
+        <v>553290</v>
       </c>
       <c r="R7" t="n">
-        <v>6835224</v>
+        <v>6835221</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1463,15 +1404,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95264257</v>
+        <v>95264089</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1498,7 +1434,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1523,13 +1459,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553278</v>
+        <v>553285</v>
       </c>
       <c r="R8" t="n">
-        <v>6835221</v>
+        <v>6835208</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1596,15 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95263872</v>
+        <v>95264194</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,7 +1562,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1652,14 +1583,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
+          <t>Grönås !9:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553298</v>
+        <v>553285</v>
       </c>
       <c r="R9" t="n">
-        <v>6835194</v>
+        <v>6835224</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1729,15 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95386244</v>
+        <v>95264257</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1690,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1778,17 +1704,21 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553144</v>
+        <v>553278</v>
       </c>
       <c r="R10" t="n">
-        <v>6835158</v>
+        <v>6835221</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1833,6 +1763,16 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1841,22 +1781,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95386183</v>
+        <v>95264356</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,7 +1818,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1897,20 +1832,24 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553168</v>
+        <v>553080</v>
       </c>
       <c r="R11" t="n">
-        <v>6835167</v>
+        <v>6835220</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1940,6 +1879,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Förutom de blommande stjälkarna, en stor yta marktäckande bladrosetter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1952,6 +1896,16 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -1960,22 +1914,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95386114</v>
+        <v>95264424</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2002,7 +1951,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2016,20 +1965,24 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553307</v>
+        <v>553093</v>
       </c>
       <c r="R12" t="n">
-        <v>6835216</v>
+        <v>6835043</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2059,11 +2012,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5 Knärot i blom och många bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2076,6 +2024,16 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
@@ -2084,22 +2042,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95386099</v>
+        <v>95264460</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2126,7 +2079,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2140,17 +2093,21 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553304</v>
+        <v>553241</v>
       </c>
       <c r="R13" t="n">
-        <v>6835208</v>
+        <v>6835143</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2195,6 +2152,16 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
@@ -2203,22 +2170,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95386259</v>
+        <v>95264522</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2245,7 +2207,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2259,17 +2221,21 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553129</v>
+        <v>553269</v>
       </c>
       <c r="R14" t="n">
-        <v>6835170</v>
+        <v>6835143</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2314,6 +2280,16 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
@@ -2322,22 +2298,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95386456</v>
+        <v>95386099</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2364,7 +2335,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2385,13 +2356,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553248</v>
+        <v>553304</v>
       </c>
       <c r="R15" t="n">
-        <v>6835176</v>
+        <v>6835208</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2421,11 +2392,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>29 blommande Knärot i utspridda kolonier.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2453,15 +2419,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>95386154</v>
+        <v>95386114</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2488,7 +2449,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2509,10 +2470,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553256</v>
+        <v>553307</v>
       </c>
       <c r="R16" t="n">
-        <v>6835309</v>
+        <v>6835216</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2549,7 +2510,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>9 Knärot i blom, nästan marktäckande.</t>
+          <t>5 Knärot i blom och många bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2570,22 +2531,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>95386313</v>
+        <v>95386133</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2612,7 +2568,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2633,10 +2589,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553052</v>
+        <v>553305</v>
       </c>
       <c r="R17" t="n">
-        <v>6835132</v>
+        <v>6835219</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2673,7 +2629,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>65 blommande Knärot på ca 1 m2</t>
+          <t>1 Knärot i blomm och många bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2701,15 +2657,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95386133</v>
+        <v>95386154</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2687,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2757,10 +2708,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553305</v>
+        <v>553256</v>
       </c>
       <c r="R18" t="n">
-        <v>6835219</v>
+        <v>6835309</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2797,7 +2748,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 Knärot i blomm och många bladrosetter</t>
+          <t>9 Knärot i blom, nästan marktäckande.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2818,22 +2769,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>95386487</v>
+        <v>95386183</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2860,7 +2806,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2881,10 +2827,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553258</v>
+        <v>553168</v>
       </c>
       <c r="R19" t="n">
-        <v>6835177</v>
+        <v>6835167</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2944,15 +2890,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>95264356</v>
+        <v>95386200</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2920,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2993,24 +2934,20 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553080</v>
+        <v>553166</v>
       </c>
       <c r="R20" t="n">
-        <v>6835220</v>
+        <v>6835162</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3040,11 +2977,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Förutom de blommande stjälkarna, en stor yta marktäckande bladrosetter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3057,16 +2989,6 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
@@ -3075,22 +2997,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>95386500</v>
+        <v>95386224</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3117,7 +3034,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3138,10 +3055,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553256</v>
+        <v>553160</v>
       </c>
       <c r="R21" t="n">
-        <v>6835183</v>
+        <v>6835145</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3174,6 +3091,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>17 blommande Knärot, ymnigt med bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3201,42 +3123,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>95386164</v>
+        <v>95386244</v>
       </c>
       <c r="B22" t="n">
-        <v>95335</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3245,10 +3174,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>553236</v>
+        <v>553144</v>
       </c>
       <c r="R22" t="n">
-        <v>6835358</v>
+        <v>6835158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3301,57 +3230,56 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>95264703</v>
+        <v>95386259</v>
       </c>
       <c r="B23" t="n">
-        <v>95335</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3360,10 +3288,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>553102</v>
+        <v>553129</v>
       </c>
       <c r="R23" t="n">
-        <v>6835064</v>
+        <v>6835170</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3408,16 +3336,6 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
-        </is>
-      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
@@ -3426,22 +3344,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95264424</v>
+        <v>95386313</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3468,7 +3381,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>65</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3482,24 +3395,20 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>553093</v>
+        <v>553052</v>
       </c>
       <c r="R24" t="n">
-        <v>6835043</v>
+        <v>6835132</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3529,6 +3438,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>65 blommande Knärot på ca 1 m2</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3541,16 +3455,6 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
-        </is>
-      </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
@@ -3559,22 +3463,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95386390</v>
+        <v>95386375</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3601,7 +3500,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3622,10 +3521,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>553215</v>
+        <v>553200</v>
       </c>
       <c r="R25" t="n">
-        <v>6835153</v>
+        <v>6835111</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3685,15 +3584,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>95386224</v>
+        <v>95386390</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3720,7 +3614,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3741,10 +3635,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>553160</v>
+        <v>553215</v>
       </c>
       <c r="R26" t="n">
-        <v>6835145</v>
+        <v>6835153</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3777,11 +3671,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>17 blommande Knärot, ymnigt med bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3809,15 +3698,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95386517</v>
+        <v>95386456</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3844,7 +3728,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3865,13 +3749,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>553280</v>
+        <v>553248</v>
       </c>
       <c r="R27" t="n">
-        <v>6835189</v>
+        <v>6835176</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3905,7 +3789,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>23 blommande Knärot i utspridda kolonier</t>
+          <t>29 blommande Knärot i utspridda kolonier.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3933,15 +3817,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95263753</v>
+        <v>95386474</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3968,7 +3847,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3982,24 +3861,20 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grönås 19:1 Vid Rotfarsdalen, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>553297</v>
+        <v>553258</v>
       </c>
       <c r="R28" t="n">
-        <v>6835193</v>
+        <v>6835177</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4029,11 +3904,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2021-08-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>28 blommande stjälkar inom ca 20 m2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4045,16 +3915,6 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Brandpräglad kontinuitetsskog, barrskog med huvudsakligen gran, frisk blåbärstyp, rikt mosstäcke, delvis luckig, relativt gott om död ved, stående och liggande, sluttande mot myr.</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4071,15 +3931,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95386200</v>
+        <v>95386500</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4127,10 +3982,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>553166</v>
+        <v>553256</v>
       </c>
       <c r="R29" t="n">
-        <v>6835162</v>
+        <v>6835183</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4190,15 +4045,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>95386375</v>
+        <v>95386517</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4225,7 +4075,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4246,10 +4096,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>553200</v>
+        <v>553280</v>
       </c>
       <c r="R30" t="n">
-        <v>6835111</v>
+        <v>6835189</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4282,6 +4132,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-08-02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>23 blommande Knärot i utspridda kolonier</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4312,12 +4167,7 @@
         <v>97976738</v>
       </c>
       <c r="B31" t="n">
-        <v>79851</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 12105-2023 artfynd.xlsx
+++ b/artfynd/A 12105-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264703</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95263400</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95263753</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1273,6 +1298,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95263872</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1401,6 +1431,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264049</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1529,6 +1564,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264089</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1657,6 +1697,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264194</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1785,6 +1830,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264257</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1918,6 +1968,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264356</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2046,6 +2101,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264424</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2174,6 +2234,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264460</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2302,6 +2367,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95264522</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2416,6 +2486,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386099</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2535,6 +2610,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386114</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2654,6 +2734,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386133</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2773,6 +2858,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386154</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2887,6 +2977,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386183</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3001,6 +3096,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386200</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3120,6 +3220,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386224</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3234,6 +3339,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386244</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3348,6 +3458,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386259</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3467,6 +3582,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386313</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3581,6 +3701,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386375</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3695,6 +3820,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386390</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3814,6 +3944,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386456</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3928,6 +4063,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386474</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4042,6 +4182,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386500</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4161,6 +4306,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95386517</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4285,8 +4435,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97976738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>